--- a/Versão5/CSUS/Ontologia_CSUS_2Q.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_2Q.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DE789B-6194-4449-9958-2410628303BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A65455-AFB4-448F-A793-66C47F87EBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21220" uniqueCount="1899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21220" uniqueCount="1898">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -5697,15 +5697,9 @@
     <t>"Equipamento do SUS"</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
-    <t>Arquitetura</t>
-  </si>
-  <si>
     <t>[ 5I ]</t>
   </si>
   <si>
@@ -5791,6 +5785,9 @@
   </si>
   <si>
     <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
   </si>
 </sst>
 </file>
@@ -7063,7 +7060,7 @@
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46233.492513888887</v>
+        <v>46243.445977083335</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>1805</v>
@@ -7162,10 +7159,10 @@
     </row>
     <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="B27" s="70" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="C27" s="48" t="s">
         <v>1805</v>
@@ -7173,10 +7170,10 @@
     </row>
     <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="C28" s="48" t="s">
         <v>1805</v>
@@ -7184,10 +7181,10 @@
     </row>
     <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="B29" s="71" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="C29" s="48" t="s">
         <v>1805</v>
@@ -7195,10 +7192,10 @@
     </row>
     <row r="30" spans="1:3" s="67" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="B30" s="72" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="C30" s="48" t="s">
         <v>1805</v>
@@ -7206,10 +7203,10 @@
     </row>
     <row r="31" spans="1:3" s="67" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="B31" s="72" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="C31" s="48" t="s">
         <v>1805</v>
@@ -7217,10 +7214,10 @@
     </row>
     <row r="32" spans="1:3" s="67" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="B32" s="72" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="C32" s="48" t="s">
         <v>1805</v>
@@ -7228,10 +7225,10 @@
     </row>
     <row r="33" spans="1:3" s="67" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="17" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="B33" s="68" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="C33" s="48" t="s">
         <v>1805</v>
@@ -7239,10 +7236,10 @@
     </row>
     <row r="34" spans="1:3" s="67" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="17" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="B34" s="68" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="C34" s="48" t="s">
         <v>1805</v>
@@ -7250,10 +7247,10 @@
     </row>
     <row r="35" spans="1:3" s="67" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="B35" s="72" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="C35" s="48" t="s">
         <v>1805</v>
@@ -7261,10 +7258,10 @@
     </row>
     <row r="36" spans="1:3" s="67" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="B36" s="68" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="C36" s="48" t="s">
         <v>1805</v>
@@ -7272,10 +7269,10 @@
     </row>
     <row r="37" spans="1:3" s="67" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="17" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="B37" s="72" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="C37" s="48" t="s">
         <v>1805</v>
@@ -7283,10 +7280,10 @@
     </row>
     <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="B38" s="73" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="C38" s="48" t="s">
         <v>1805</v>
@@ -7294,10 +7291,10 @@
     </row>
     <row r="39" spans="1:3" s="69" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="17" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="B39" s="74" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="C39" s="48" t="s">
         <v>1805</v>
@@ -7305,10 +7302,10 @@
     </row>
     <row r="40" spans="1:3" s="16" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="17" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="B40" s="74" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="C40" s="48" t="s">
         <v>1805</v>
@@ -7334,8 +7331,8 @@
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.69921875" style="16" customWidth="1"/>
-    <col min="2" max="2" width="5.296875" style="22" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.8984375" style="22" customWidth="1"/>
+    <col min="3" max="3" width="6.796875" style="16" customWidth="1"/>
     <col min="4" max="4" width="14" style="16" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="16" customWidth="1"/>
     <col min="6" max="6" width="13.19921875" style="16" customWidth="1"/>
@@ -7446,7 +7443,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C2" s="57" t="s">
         <v>1835</v>
@@ -7455,7 +7452,7 @@
         <v>1119</v>
       </c>
       <c r="E2" s="58" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="F2" s="58" t="s">
         <v>1120</v>
@@ -7513,7 +7510,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="53" t="s">
-        <v>1869</v>
+        <v>1836</v>
       </c>
       <c r="W2" s="66" t="str">
         <f t="shared" ref="W2:W27" si="3">CONCATENATE("Key-SUS-",A2)</f>
@@ -7526,7 +7523,7 @@
         <v>25</v>
       </c>
       <c r="Z2" s="54" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="AA2" s="53" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -7538,7 +7535,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C3" s="57" t="s">
         <v>1835</v>
@@ -7547,7 +7544,7 @@
         <v>1119</v>
       </c>
       <c r="E3" s="58" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="F3" s="58" t="s">
         <v>1837</v>
@@ -7605,7 +7602,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="53" t="s">
-        <v>1869</v>
+        <v>1836</v>
       </c>
       <c r="W3" s="66" t="str">
         <f t="shared" si="3"/>
@@ -7630,7 +7627,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>1835</v>
@@ -7639,7 +7636,7 @@
         <v>1119</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="F4" s="58" t="s">
         <v>1839</v>
@@ -7697,7 +7694,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="53" t="s">
-        <v>1869</v>
+        <v>1836</v>
       </c>
       <c r="W4" s="66" t="str">
         <f t="shared" si="3"/>
@@ -7722,7 +7719,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C5" s="57" t="s">
         <v>1835</v>
@@ -7731,7 +7728,7 @@
         <v>1119</v>
       </c>
       <c r="E5" s="58" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="F5" s="58" t="s">
         <v>1841</v>
@@ -7789,7 +7786,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="53" t="s">
-        <v>1869</v>
+        <v>1836</v>
       </c>
       <c r="W5" s="66" t="str">
         <f t="shared" si="3"/>
@@ -7814,7 +7811,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C6" s="57" t="s">
         <v>1835</v>
@@ -7823,7 +7820,7 @@
         <v>1119</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="F6" s="58" t="s">
         <v>1843</v>
@@ -7881,7 +7878,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="53" t="s">
-        <v>1869</v>
+        <v>1836</v>
       </c>
       <c r="W6" s="66" t="str">
         <f t="shared" si="3"/>
@@ -7906,7 +7903,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C7" s="58" t="s">
         <v>1083</v>
@@ -7998,7 +7995,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C8" s="58" t="s">
         <v>1083</v>
@@ -8090,7 +8087,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C9" s="58" t="s">
         <v>1083</v>
@@ -8182,7 +8179,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C10" s="58" t="s">
         <v>1083</v>
@@ -8274,7 +8271,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>1083</v>
@@ -8366,7 +8363,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C12" s="58" t="s">
         <v>1083</v>
@@ -8458,7 +8455,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C13" s="58" t="s">
         <v>1083</v>
@@ -8550,7 +8547,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C14" s="58" t="s">
         <v>1083</v>
@@ -8642,7 +8639,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>1083</v>
@@ -8734,7 +8731,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C16" s="58" t="s">
         <v>1083</v>
@@ -8826,7 +8823,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C17" s="58" t="s">
         <v>1083</v>
@@ -8918,7 +8915,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>1083</v>
@@ -9010,7 +9007,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C19" s="58" t="s">
         <v>1083</v>
@@ -9102,7 +9099,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C20" s="58" t="s">
         <v>1083</v>
@@ -9194,7 +9191,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C21" s="58" t="s">
         <v>1083</v>
@@ -9286,7 +9283,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C22" s="58" t="s">
         <v>1083</v>
@@ -9378,7 +9375,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C23" s="58" t="s">
         <v>1083</v>
@@ -9470,7 +9467,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C24" s="58" t="s">
         <v>1083</v>
@@ -9562,7 +9559,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C25" s="58" t="s">
         <v>1083</v>
@@ -9654,7 +9651,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C26" s="58" t="s">
         <v>1083</v>
@@ -9746,7 +9743,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="57" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="C27" s="58" t="s">
         <v>1083</v>
@@ -9840,7 +9837,7 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:F27 L7:Q27">
+  <conditionalFormatting sqref="L7:Q27 D7:F27">
     <cfRule type="cellIs" dxfId="20" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -9862,7 +9859,7 @@
     <cfRule type="duplicateValues" dxfId="10" priority="19"/>
     <cfRule type="duplicateValues" dxfId="9" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z7:XFD7 S7:V27 X8:XFD17 Z18:XFD19 X20:XFD27">
+  <conditionalFormatting sqref="Z7:XFD7 S7:U27 X8:XFD17 Z18:XFD19 X20:XFD27 V2:V27">
     <cfRule type="cellIs" dxfId="8" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
